--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_ingr_mean_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_ingr_mean_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:43</t>
+    <t xml:space="preserve">2026-09-18 09:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_ingr_mean_a_2021_nacional.xlsx
+++ b/output/graficos_regionales_sexo_edad/plot_historia_nacional_i_ingr_mean_a_2021_nacional.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 09:03</t>
+    <t xml:space="preserve">2026-10-05 04:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>420623.12</v>
+        <v>420623.13</v>
       </c>
     </row>
     <row r="11">
@@ -862,7 +862,7 @@
         <v>19</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>567776.12</v>
+        <v>567776.13</v>
       </c>
     </row>
     <row r="15">
@@ -884,7 +884,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>537825.62</v>
+        <v>537825.63</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>601748.62</v>
+        <v>601748.63</v>
       </c>
     </row>
     <row r="20">
@@ -939,7 +939,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>754159.12</v>
+        <v>754159.13</v>
       </c>
     </row>
     <row r="22">
